--- a/workbook/overrides.xlsx
+++ b/workbook/overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,6 +1059,133 @@
       <c r="N10" t="inlineStr">
         <is>
           <t>2026-09-28 23:27:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0036cf7c6f04</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>沛公</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>【沛公】拜勃爲襄賁令。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>p_xiangyu</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reassign</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:37:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0072cad670bc</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>漢王</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>時【漢王】還定三秦，良乃遺項羽書曰：「</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:37:19</t>
         </is>
       </c>
     </row>

--- a/workbook/overrides.xlsx
+++ b/workbook/overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1189,6 +1189,260 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0036cf7c6f04</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>沛公</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>【沛公】拜勃爲襄賁令。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>p_xiangyu</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reassign</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0072cad670bc</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>漢王</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>時【漢王】還定三秦，良乃遺項羽書曰：「</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0036cf7c6f04</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>沛公</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>【沛公】拜勃爲襄賁令。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>p_xiangyu</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reassign</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:21:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0072cad670bc</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>漢王</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>時【漢王】還定三秦，良乃遺項羽書曰：「</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:21:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbook/overrides.xlsx
+++ b/workbook/overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,260 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0036cf7c6f04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>沛公</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>【沛公】拜勃爲襄賁令。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>p_xiangyu</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reassign</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:34:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0072cad670bc</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>漢王</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>時【漢王】還定三秦，良乃遺項羽書曰：「</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:34:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0036cf7c6f04</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>沛公</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>【沛公】拜勃爲襄賁令。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>p_xiangyu</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reassign</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:38:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0072cad670bc</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>漢王</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>時【漢王】還定三秦，良乃遺項羽書曰：「</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:38:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbook/overrides.xlsx
+++ b/workbook/overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1697,6 +1697,133 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0036cf7c6f04</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>沛公</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>【沛公】拜勃爲襄賁令。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>p_xiangyu</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>reassign</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0072cad670bc</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>漢王</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>hs-040</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>時【漢王】還定三秦，良乃遺項羽書曰：「</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>p_liubang</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>P3-5 自檢</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:19:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
